--- a/data/trans_orig/P6605-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6605-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116967</t>
+          <t>117542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154016</t>
+          <t>154915</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>69462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99623</t>
+          <t>98389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195545</t>
+          <t>194816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242296</t>
+          <t>241412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82127</t>
+          <t>82438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116236</t>
+          <t>117744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53117</t>
+          <t>52308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80587</t>
+          <t>79375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145605</t>
+          <t>146139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>189367</t>
+          <t>187576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>62276</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94553</t>
+          <t>94129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35319</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59885</t>
+          <t>59946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104405</t>
+          <t>102987</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>144652</t>
+          <t>142711</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>63520</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49704</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82335</t>
+          <t>81452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89345</t>
+          <t>88057</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122892</t>
+          <t>121138</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62989</t>
+          <t>62811</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91393</t>
+          <t>91475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>160712</t>
+          <t>161383</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>205569</t>
+          <t>205422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59538</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90283</t>
+          <t>89500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69835</t>
+          <t>69542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111454</t>
+          <t>109861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150494</t>
+          <t>151112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50403</t>
+          <t>51581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79199</t>
+          <t>79368</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>47212</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>73664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105960</t>
+          <t>106597</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146028</t>
+          <t>144562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37900</t>
+          <t>37647</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>28091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50152</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>50054</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80213</t>
+          <t>80268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81986</t>
+          <t>83739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118352</t>
+          <t>117178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94740</t>
+          <t>94298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131660</t>
+          <t>131275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72884</t>
+          <t>73498</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107323</t>
+          <t>106269</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>92449</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>130512</t>
+          <t>128588</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78903</t>
+          <t>77223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114091</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22049</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90460</t>
+          <t>92353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128438</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79855</t>
+          <t>79870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115060</t>
+          <t>115038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89098</t>
+          <t>88711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127616</t>
+          <t>124876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>127681</t>
+          <t>126459</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172193</t>
+          <t>170059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79215</t>
+          <t>80431</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112385</t>
+          <t>113192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>216892</t>
+          <t>217900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>274295</t>
+          <t>273774</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119904</t>
+          <t>119967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164170</t>
+          <t>162880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56628</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86686</t>
+          <t>87903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>184817</t>
+          <t>187268</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239615</t>
+          <t>240085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189181</t>
+          <t>187727</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240241</t>
+          <t>237384</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73196</t>
+          <t>73854</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107691</t>
+          <t>105709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>272599</t>
+          <t>272377</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>330607</t>
+          <t>328430</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180989</t>
+          <t>180652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>230725</t>
+          <t>229012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38451</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64325</t>
+          <t>64859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227343</t>
+          <t>225871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>283844</t>
+          <t>283286</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>42160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>35315</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59527</t>
+          <t>60873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62094</t>
+          <t>61893</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93460</t>
+          <t>95363</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>43839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43889</t>
+          <t>43712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>50576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81400</t>
+          <t>82654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>41271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67813</t>
+          <t>67772</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49390</t>
+          <t>48973</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76604</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>96896</t>
+          <t>96418</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133796</t>
+          <t>135480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56263</t>
+          <t>53845</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>83195</t>
+          <t>82344</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56926</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>84795</t>
+          <t>85113</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>118874</t>
+          <t>119822</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>157554</t>
+          <t>158439</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>478620</t>
+          <t>478118</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>556388</t>
+          <t>557452</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>287696</t>
+          <t>286154</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>346778</t>
+          <t>346328</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>784251</t>
+          <t>787556</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>883992</t>
+          <t>886148</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>396121</t>
+          <t>399675</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>469790</t>
+          <t>478206</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>218532</t>
+          <t>222120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>275727</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>630293</t>
+          <t>636517</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>730765</t>
+          <t>732964</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>465527</t>
+          <t>459594</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>544418</t>
+          <t>542875</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>245867</t>
+          <t>242177</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>300873</t>
+          <t>301902</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>724008</t>
+          <t>728312</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>824847</t>
+          <t>825686</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>408184</t>
+          <t>406149</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>481204</t>
+          <t>479835</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>162162</t>
+          <t>162820</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>212380</t>
+          <t>213322</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>583704</t>
+          <t>584759</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>676211</t>
+          <t>673824</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80829</t>
+          <t>79702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113740</t>
+          <t>114290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58141</t>
+          <t>56809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86846</t>
+          <t>86021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>146236</t>
+          <t>145461</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188780</t>
+          <t>189403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63805</t>
+          <t>64693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97053</t>
+          <t>97427</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47557</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74662</t>
+          <t>73268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>118941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163267</t>
+          <t>160667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66911</t>
+          <t>66280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56314</t>
+          <t>56422</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>106644</t>
+          <t>104299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>145160</t>
+          <t>144766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>14279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31501</t>
+          <t>32429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50526</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82255</t>
+          <t>82620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69874</t>
+          <t>72315</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>104279</t>
+          <t>105174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44355</t>
+          <t>44859</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>70385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123511</t>
+          <t>123465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>165891</t>
+          <t>163325</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57204</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87406</t>
+          <t>87595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31510</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54642</t>
+          <t>54962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95094</t>
+          <t>96923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133487</t>
+          <t>134637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51707</t>
+          <t>52376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81687</t>
+          <t>85246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20175</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>41193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77400</t>
+          <t>78026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115577</t>
+          <t>114235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44058</t>
+          <t>43836</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50626</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44851</t>
+          <t>44404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73110</t>
+          <t>70868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35102</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67605</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100753</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55025</t>
+          <t>53697</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81691</t>
+          <t>81060</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>79588</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>114664</t>
+          <t>114004</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81442</t>
+          <t>83268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113519</t>
+          <t>115378</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>105891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143486</t>
+          <t>143650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43881</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71617</t>
+          <t>72633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>41231</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72126</t>
+          <t>71457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105349</t>
+          <t>105525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55715</t>
+          <t>56110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86440</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57003</t>
+          <t>58259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88314</t>
+          <t>88225</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121434</t>
+          <t>122445</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167255</t>
+          <t>166395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>85628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123422</t>
+          <t>122351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61564</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92250</t>
+          <t>92855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>156279</t>
+          <t>158296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203492</t>
+          <t>207371</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>103344</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>140799</t>
+          <t>140776</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64560</t>
+          <t>64005</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94152</t>
+          <t>95611</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>177499</t>
+          <t>178348</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>228055</t>
+          <t>226477</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108413</t>
+          <t>108340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147017</t>
+          <t>145553</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57133</t>
+          <t>58158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87411</t>
+          <t>87745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>174765</t>
+          <t>174588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222341</t>
+          <t>221698</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>29126</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53993</t>
+          <t>53673</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18316</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58879</t>
+          <t>59624</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59580</t>
+          <t>56517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89064</t>
+          <t>87611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66149</t>
+          <t>67294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44302</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69357</t>
+          <t>70135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93350</t>
+          <t>93666</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>128263</t>
+          <t>129591</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>43935</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>69270</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>35295</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60348</t>
+          <t>60523</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>87231</t>
+          <t>86622</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>122094</t>
+          <t>122515</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>294010</t>
+          <t>295078</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>358546</t>
+          <t>364178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>226132</t>
+          <t>222019</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>281686</t>
+          <t>282144</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>532247</t>
+          <t>535641</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>620849</t>
+          <t>618748</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>316338</t>
+          <t>316876</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>385070</t>
+          <t>387111</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>223771</t>
+          <t>223201</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>280337</t>
+          <t>280313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>561531</t>
+          <t>561006</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>649722</t>
+          <t>646728</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>386194</t>
+          <t>390120</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>459025</t>
+          <t>460532</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>205825</t>
+          <t>208750</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>262483</t>
+          <t>265606</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>612895</t>
+          <t>613613</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>702077</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>284974</t>
+          <t>283954</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>352539</t>
+          <t>348894</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>182016</t>
+          <t>184266</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>236733</t>
+          <t>239466</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>482274</t>
+          <t>485181</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>565868</t>
+          <t>567264</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123277</t>
+          <t>123953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156469</t>
+          <t>158331</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80248</t>
+          <t>81262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110045</t>
+          <t>110766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>213340</t>
+          <t>213372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>259844</t>
+          <t>256376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51664</t>
+          <t>50905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80550</t>
+          <t>79793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>34983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93782</t>
+          <t>92760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131941</t>
+          <t>130597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34947</t>
+          <t>33913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60687</t>
+          <t>59748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>31815</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>72154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108873</t>
+          <t>107361</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37827</t>
+          <t>37003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>42284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70069</t>
+          <t>72321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -8596,12 +8596,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81720</t>
+          <t>81544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>115065</t>
+          <t>114820</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>80324</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>109170</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>171744</t>
+          <t>171560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>211892</t>
+          <t>212571</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51388</t>
+          <t>51245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80982</t>
+          <t>80245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35394</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59158</t>
+          <t>59374</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93365</t>
+          <t>93421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130937</t>
+          <t>130689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39694</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66240</t>
+          <t>65841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38381</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63121</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96777</t>
+          <t>95219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -8935,12 +8935,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28261</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>35766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62657</t>
+          <t>62747</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36632</t>
+          <t>35732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61692</t>
+          <t>60964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50267</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79632</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58237</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86417</t>
+          <t>86424</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>22997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>70179</t>
+          <t>71441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103301</t>
+          <t>102879</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9391,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53762</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81756</t>
+          <t>80636</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69976</t>
+          <t>69168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101542</t>
+          <t>100237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41638</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60174</t>
+          <t>62003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89465</t>
+          <t>87172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124872</t>
+          <t>126234</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89614</t>
+          <t>89981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122645</t>
+          <t>122934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186756</t>
+          <t>188583</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238658</t>
+          <t>239524</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>89513</t>
+          <t>88541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126618</t>
+          <t>126585</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78710</t>
+          <t>77631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110959</t>
+          <t>111001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177316</t>
+          <t>176133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228121</t>
+          <t>227916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>126326</t>
+          <t>126295</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>167208</t>
+          <t>165228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68737</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>100562</t>
+          <t>99722</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>204229</t>
+          <t>205437</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>258057</t>
+          <t>256886</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106560</t>
+          <t>108275</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145713</t>
+          <t>148678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>67640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100815</t>
+          <t>99963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181689</t>
+          <t>182629</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>234597</t>
+          <t>236043</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28590</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39111</t>
+          <t>37620</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33579</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57832</t>
+          <t>58720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48190</t>
+          <t>47417</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74321</t>
+          <t>73287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10466,12 +10466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83136</t>
+          <t>83802</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117228</t>
+          <t>117450</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60160</t>
+          <t>59690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87112</t>
+          <t>87620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42903</t>
+          <t>42313</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67134</t>
+          <t>66998</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>108714</t>
+          <t>109326</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146204</t>
+          <t>146010</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49688</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>75698</t>
+          <t>77499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>43902</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>100609</t>
+          <t>101073</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>138988</t>
+          <t>139590</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>379801</t>
+          <t>378616</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>447148</t>
+          <t>446893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>312106</t>
+          <t>309126</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>369273</t>
+          <t>370998</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>705140</t>
+          <t>705783</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>798534</t>
+          <t>798549</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>315524</t>
+          <t>316145</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>382474</t>
+          <t>382817</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11000,12 +11000,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>232697</t>
+          <t>235938</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>287914</t>
+          <t>291002</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>561640</t>
+          <t>569757</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>657754</t>
+          <t>654120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>346295</t>
+          <t>348683</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>417012</t>
+          <t>418033</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11113,49 +11113,49 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>227517</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>199527</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>253351</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>24,52%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>29,52%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>227517</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>201027</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>254061</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>587</t>
@@ -11168,12 +11168,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>568965</t>
+          <t>569856</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>651752</t>
+          <t>652897</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>239442</t>
+          <t>241198</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>300797</t>
+          <t>302350</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>179842</t>
+          <t>179427</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>233376</t>
+          <t>232975</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>439439</t>
+          <t>432660</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>518723</t>
+          <t>518403</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -11669,32 +11669,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>104295</t>
+          <t>118851</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90144</t>
+          <t>103045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118201</t>
+          <t>134182</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11704,32 +11704,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76329</t>
+          <t>83025</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65506</t>
+          <t>71776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86535</t>
+          <t>93395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11739,32 +11739,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>180624</t>
+          <t>201877</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163761</t>
+          <t>181478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>197666</t>
+          <t>219833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,9%</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11782,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33898</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>26806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44856</t>
+          <t>50090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11817,32 +11817,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>41664</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>32271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48072</t>
+          <t>51082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11852,32 +11852,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>72094</t>
+          <t>78344</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58538</t>
+          <t>65052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86224</t>
+          <t>93844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -11895,32 +11895,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22089</t>
+          <t>21793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43406</t>
+          <t>43474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11930,32 +11930,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11965,32 +11965,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>48543</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36555</t>
+          <t>36570</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63088</t>
+          <t>62280</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>12937</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>29175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>32212</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12121,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12156,17 +12156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12238,32 +12238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60519</t>
+          <t>65540</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48606</t>
+          <t>52173</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72790</t>
+          <t>78882</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12273,32 +12273,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>50749</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35670</t>
+          <t>40823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55344</t>
+          <t>61087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12308,32 +12308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>105672</t>
+          <t>116289</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>98008</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>123183</t>
+          <t>132604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -12351,32 +12351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>51207</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39542</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63681</t>
+          <t>66443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39297</t>
+          <t>41730</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>33348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>51152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12421,32 +12421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>92937</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76476</t>
+          <t>77515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108139</t>
+          <t>111143</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -12464,32 +12464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19881</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44392</t>
+          <t>41526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12499,32 +12499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27730</t>
+          <t>26503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12534,32 +12534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>36758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64325</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -12577,32 +12577,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>12042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12612,17 +12612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>31548</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -12690,17 +12690,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12760,17 +12760,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>263034</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>340842</t>
+          <t>31572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12842,32 +12842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>18963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>272907</t>
+          <t>31862</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59397</t>
+          <t>22126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>376099</t>
+          <t>46239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -12920,32 +12920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>45777</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136303</t>
+          <t>58803</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12955,32 +12955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12990,32 +12990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>54649</t>
+          <t>58712</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>46066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142537</t>
+          <t>72518</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -13033,32 +13033,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45043</t>
+          <t>48620</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141274</t>
+          <t>60367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13068,32 +13068,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>23398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13103,32 +13103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>60446</t>
+          <t>65547</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>52951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153911</t>
+          <t>79705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -13146,32 +13146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71479</t>
+          <t>40258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13181,32 +13181,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>35663</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>24594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78848</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13294,17 +13294,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13329,17 +13329,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13376,32 +13376,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>43805</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49609</t>
+          <t>58892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13411,32 +13411,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>44409</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28663</t>
+          <t>34519</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49450</t>
+          <t>56247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13446,32 +13446,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>73527</t>
+          <t>88213</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58664</t>
+          <t>72205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89086</t>
+          <t>108011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -13489,32 +13489,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>75455</t>
+          <t>82514</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60838</t>
+          <t>67180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92464</t>
+          <t>100319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13524,32 +13524,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>68570</t>
+          <t>74190</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>61904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81771</t>
+          <t>87942</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13559,32 +13559,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>144025</t>
+          <t>156704</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124973</t>
+          <t>137139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164365</t>
+          <t>178657</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -13602,32 +13602,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>112533</t>
+          <t>123300</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95981</t>
+          <t>105891</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>142488</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13637,32 +13637,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56473</t>
+          <t>64337</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68385</t>
+          <t>77448</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13672,32 +13672,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>169006</t>
+          <t>187638</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>147984</t>
+          <t>165159</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>191283</t>
+          <t>209195</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -13715,32 +13715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>39286</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22885</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>55002</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13750,32 +13750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26748</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>49772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13785,32 +13785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>69453</t>
+          <t>78279</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86734</t>
+          <t>96434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -13828,17 +13828,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>257484</t>
+          <t>288906</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>257484</t>
+          <t>288906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>257484</t>
+          <t>288906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13863,17 +13863,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13898,17 +13898,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>456011</t>
+          <t>510834</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>456011</t>
+          <t>510834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>456011</t>
+          <t>510834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13945,32 +13945,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>41758</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13980,32 +13980,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14015,32 +14015,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>43325</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21695</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48036</t>
+          <t>59625</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -14058,32 +14058,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>29700</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14093,32 +14093,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33760</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>29923</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45585</t>
+          <t>48025</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14128,32 +14128,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>61872</t>
+          <t>68341</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43333</t>
+          <t>55194</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78879</t>
+          <t>82459</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -14171,32 +14171,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>45704</t>
+          <t>56941</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33953</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59676</t>
+          <t>71346</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14206,32 +14206,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>47506</t>
+          <t>55650</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>24037</t>
+          <t>45610</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63384</t>
+          <t>66073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14241,32 +14241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>93210</t>
+          <t>112591</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62830</t>
+          <t>94103</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114744</t>
+          <t>129176</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38861</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>42795</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14319,32 +14319,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>67540</t>
+          <t>42856</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39879</t>
+          <t>33095</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>109698</t>
+          <t>54254</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>106401</t>
+          <t>99112</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>76975</t>
+          <t>81828</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>164203</t>
+          <t>119144</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -14397,17 +14397,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14432,17 +14432,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14467,17 +14467,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14514,32 +14514,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>483272</t>
+          <t>274534</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>295741</t>
+          <t>244861</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>782457</t>
+          <t>312212</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14549,32 +14549,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>183098</t>
+          <t>207033</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>154103</t>
+          <t>186012</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>205788</t>
+          <t>229048</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14584,32 +14584,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>666370</t>
+          <t>481567</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>479083</t>
+          <t>438401</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1105051</t>
+          <t>520137</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -14627,32 +14627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>230682</t>
+          <t>245878</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117374</t>
+          <t>217165</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>310586</t>
+          <t>276050</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14662,32 +14662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>191873</t>
+          <t>209160</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>155743</t>
+          <t>189032</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>215066</t>
+          <t>230516</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14697,32 +14697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>422555</t>
+          <t>455039</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>255077</t>
+          <t>420285</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>505344</t>
+          <t>494183</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -14740,32 +14740,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>263690</t>
+          <t>289949</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>137388</t>
+          <t>259223</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>351792</t>
+          <t>323995</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14775,32 +14775,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>156615</t>
+          <t>173094</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>127179</t>
+          <t>153262</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>176970</t>
+          <t>195407</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14810,32 +14810,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>420305</t>
+          <t>463043</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>251458</t>
+          <t>426632</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>505446</t>
+          <t>501804</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -14853,32 +14853,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>124425</t>
+          <t>156233</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>131605</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>171520</t>
+          <t>188181</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14888,32 +14888,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>141113</t>
+          <t>122575</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>107215</t>
+          <t>105308</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>243585</t>
+          <t>140957</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14923,32 +14923,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>265538</t>
+          <t>278808</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>177553</t>
+          <t>248858</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>344532</t>
+          <t>316628</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -14966,17 +14966,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1102069</t>
+          <t>966595</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1102069</t>
+          <t>966595</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1102069</t>
+          <t>966595</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15036,17 +15036,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1774768</t>
+          <t>1678457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1774768</t>
+          <t>1678457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1774768</t>
+          <t>1678457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
